--- a/tests/fixtures/format_francais.xlsx
+++ b/tests/fixtures/format_francais.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,12 +458,63 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Le fournisseur doit livrer la documentation complète avant la recette usine.</t>
+          <t>Le fournisseur doit livrer la documentation complète avant la recette usine, dans les délais contractuels.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Exigence contractuelle</t>
+          <t>Exigence technique</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FR-003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Le dispositif de freinage doit arrêter le train dans une distance adaptée aux conditions de la voie.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Exigence technique</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FR-004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Les interfaces doivent être conçues de manière modulaire pour faciliter les évolutions ultérieures.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Exigence technique</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FR-005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Le système de supervision doit afficher les alarmes avec une priorité appropriée pour chaque situation.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Exigence technique</t>
         </is>
       </c>
     </row>
